--- a/Prototyping/InitialTest/2025.10.24/ThermalData.xlsx
+++ b/Prototyping/InitialTest/2025.10.24/ThermalData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Load Current</t>
   </si>
@@ -39,7 +39,40 @@
     <t>7.5</t>
   </si>
   <si>
-    <t>Output Power</t>
+    <t>23.7</t>
+  </si>
+  <si>
+    <t>difference</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
+    <t>23.85</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>24.15</t>
+  </si>
+  <si>
+    <t>1.07</t>
+  </si>
+  <si>
+    <t>24.5</t>
+  </si>
+  <si>
+    <t>1.22</t>
+  </si>
+  <si>
+    <t>25.3</t>
+  </si>
+  <si>
+    <t>1.8</t>
   </si>
 </sst>
 </file>
@@ -83,13 +116,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -371,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
@@ -382,7 +418,7 @@
     <col min="7" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -396,148 +432,224 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2">
-        <v>50</v>
-      </c>
-      <c r="C2" s="2">
-        <v>202</v>
-      </c>
-      <c r="D2" s="2">
-        <v>23</v>
-      </c>
-      <c r="G2">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="B3" s="2">
+        <v>50</v>
+      </c>
+      <c r="C3" s="2">
+        <v>195</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
       <c r="G3">
         <v>800</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="I3">
+        <f t="shared" ref="I3:I6" si="0">C4-C3</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2">
+        <v>212</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
       <c r="G4">
         <v>800</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="B5" s="2">
+        <v>50</v>
+      </c>
+      <c r="C5" s="2">
+        <v>260</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
       <c r="G5">
         <v>800</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2">
+        <v>50</v>
+      </c>
+      <c r="C6" s="2">
+        <v>300</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
       <c r="G6">
         <v>800</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="G7">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="2">
+        <v>100</v>
+      </c>
+      <c r="C8" s="2">
+        <v>450</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
       <c r="G8">
         <v>800</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2"/>
+      <c r="I8">
+        <f t="shared" ref="I8:I11" si="1">C9-C8</f>
+        <v>-450</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2">
+        <v>100</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="G9">
         <v>800</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>100</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="G10">
         <v>800</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2">
+        <v>100</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G11">
+        <v>800</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
